--- a/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,92 +421,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ngay_cong_bo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>to_chuc_phat_hanh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>linh_vuc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>loai_hinh</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>trang_thai_xep_hang</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>loai_y_kien</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ky_han</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ket_qua_xep_hang</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>trien_vong</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ma_trai_phieu</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>bao_cao_vi</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>bao_cao_en</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>bao_cao_chi_tiet</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>link_to_chuc_phat_hanh</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>issuer_id</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>to_chuc_xhtn</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>thoi_gian_scrape</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ngay_cong_bo_dt</t>
         </is>
@@ -589,10 +577,10 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="n">
         <v>46200</v>
       </c>
     </row>
@@ -653,10 +641,10 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="n">
         <v>46183</v>
       </c>
     </row>
@@ -717,10 +705,10 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="n">
         <v>46170</v>
       </c>
     </row>
@@ -793,10 +781,10 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R5" s="1" t="n">
         <v>46136</v>
       </c>
     </row>
@@ -865,10 +853,10 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R6" s="1" t="n">
         <v>46105</v>
       </c>
     </row>
@@ -937,10 +925,10 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R7" s="1" t="n">
         <v>46105</v>
       </c>
     </row>
@@ -1013,10 +1001,10 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R8" s="1" t="n">
         <v>46001</v>
       </c>
     </row>
@@ -1077,10 +1065,10 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R9" s="1" t="n">
         <v>46001</v>
       </c>
     </row>
@@ -1149,10 +1137,10 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R10" s="1" t="n">
         <v>45989</v>
       </c>
     </row>
@@ -1213,10 +1201,10 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R11" s="1" t="n">
         <v>45910</v>
       </c>
     </row>
@@ -1285,10 +1273,10 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R12" s="1" t="n">
         <v>45818</v>
       </c>
     </row>
@@ -1357,10 +1345,10 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:10</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="n">
+          <t>2026-09-18 07:51:24</t>
+        </is>
+      </c>
+      <c r="R13" s="1" t="n">
         <v>45726</v>
       </c>
     </row>

--- a/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:24</t>
+          <t>2026-09-18 08:13:38</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">

--- a/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:38</t>
+          <t>2026-09-18 08:21:28</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">

--- a/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:28</t>
+          <t>2026-09-18 08:50:02</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">

--- a/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:02</t>
+          <t>2026-09-18 09:05:42</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">

--- a/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:42</t>
+          <t>2026-09-18 09:22:51</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">

--- a/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:51</t>
+          <t>2026-09-18 13:07:02</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">
